--- a/data/nzd0322/nzd0322.xlsx
+++ b/data/nzd0322/nzd0322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P562"/>
+  <dimension ref="A1:P565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30772,6 +30772,168 @@
         <v>367.66</v>
       </c>
       <c r="P562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>384.3</v>
+      </c>
+      <c r="C563" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="D563" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="E563" t="n">
+        <v>381.52</v>
+      </c>
+      <c r="F563" t="n">
+        <v>387.41</v>
+      </c>
+      <c r="G563" t="n">
+        <v>389.4</v>
+      </c>
+      <c r="H563" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="I563" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="J563" t="n">
+        <v>385.64</v>
+      </c>
+      <c r="K563" t="n">
+        <v>385.79</v>
+      </c>
+      <c r="L563" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="M563" t="n">
+        <v>383.45</v>
+      </c>
+      <c r="N563" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="O563" t="n">
+        <v>366.85</v>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:18:39+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>384.91</v>
+      </c>
+      <c r="C564" t="n">
+        <v>367.68</v>
+      </c>
+      <c r="D564" t="n">
+        <v>376.72</v>
+      </c>
+      <c r="E564" t="n">
+        <v>381.13</v>
+      </c>
+      <c r="F564" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="G564" t="n">
+        <v>389.04</v>
+      </c>
+      <c r="H564" t="n">
+        <v>386.29</v>
+      </c>
+      <c r="I564" t="n">
+        <v>384.89</v>
+      </c>
+      <c r="J564" t="n">
+        <v>384.98</v>
+      </c>
+      <c r="K564" t="n">
+        <v>385.17</v>
+      </c>
+      <c r="L564" t="n">
+        <v>385.45</v>
+      </c>
+      <c r="M564" t="n">
+        <v>382.64</v>
+      </c>
+      <c r="N564" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="O564" t="n">
+        <v>366.33</v>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>387.82</v>
+      </c>
+      <c r="C565" t="n">
+        <v>368.04</v>
+      </c>
+      <c r="D565" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="E565" t="n">
+        <v>380.94</v>
+      </c>
+      <c r="F565" t="n">
+        <v>386.3</v>
+      </c>
+      <c r="G565" t="n">
+        <v>389</v>
+      </c>
+      <c r="H565" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="I565" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="J565" t="n">
+        <v>385.12</v>
+      </c>
+      <c r="K565" t="n">
+        <v>385.11</v>
+      </c>
+      <c r="L565" t="n">
+        <v>385.65</v>
+      </c>
+      <c r="M565" t="n">
+        <v>383.05</v>
+      </c>
+      <c r="N565" t="n">
+        <v>373.15</v>
+      </c>
+      <c r="O565" t="n">
+        <v>366.11</v>
+      </c>
+      <c r="P565" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30788,7 +30950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B570"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36491,6 +36653,36 @@
       </c>
       <c r="B570" t="n">
         <v>-0.27</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -36659,28 +36851,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1680758525013461</v>
+        <v>-0.1697989103476295</v>
       </c>
       <c r="J2" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K2" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01833508238673209</v>
+        <v>0.01888725445269246</v>
       </c>
       <c r="M2" t="n">
-        <v>7.930946412977786</v>
+        <v>7.900145360038558</v>
       </c>
       <c r="N2" t="n">
-        <v>93.90497803292079</v>
+        <v>93.43627564413484</v>
       </c>
       <c r="O2" t="n">
-        <v>9.690458092005805</v>
+        <v>9.66624413327818</v>
       </c>
       <c r="P2" t="n">
-        <v>392.0663261041808</v>
+        <v>392.0840833615973</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36741,28 +36933,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5613782551427979</v>
+        <v>0.5620141490886296</v>
       </c>
       <c r="J3" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K3" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1471992957571786</v>
+        <v>0.1487632825689811</v>
       </c>
       <c r="M3" t="n">
-        <v>8.498040853721843</v>
+        <v>8.4563671173991</v>
       </c>
       <c r="N3" t="n">
-        <v>113.3575773949612</v>
+        <v>112.757315885526</v>
       </c>
       <c r="O3" t="n">
-        <v>10.64695155408163</v>
+        <v>10.6187247768047</v>
       </c>
       <c r="P3" t="n">
-        <v>352.1681122583926</v>
+        <v>352.1615548565282</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36823,28 +37015,28 @@
         <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7632172990717385</v>
+        <v>0.7658619791175848</v>
       </c>
       <c r="J4" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K4" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2198372145202825</v>
+        <v>0.2227219783636698</v>
       </c>
       <c r="M4" t="n">
-        <v>8.76374933308716</v>
+        <v>8.728591521821482</v>
       </c>
       <c r="N4" t="n">
-        <v>128.3447161267231</v>
+        <v>127.7056072437825</v>
       </c>
       <c r="O4" t="n">
-        <v>11.32893270024688</v>
+        <v>11.30069056490719</v>
       </c>
       <c r="P4" t="n">
-        <v>353.6593857564089</v>
+        <v>353.6321083251486</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36901,28 +37093,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8977511071224961</v>
+        <v>0.9054777376070011</v>
       </c>
       <c r="J5" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K5" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3060009586793223</v>
+        <v>0.3111376028961012</v>
       </c>
       <c r="M5" t="n">
-        <v>8.398080469531905</v>
+        <v>8.388159738241777</v>
       </c>
       <c r="N5" t="n">
-        <v>113.4868514707141</v>
+        <v>113.2481630593856</v>
       </c>
       <c r="O5" t="n">
-        <v>10.65302076740274</v>
+        <v>10.6418120195475</v>
       </c>
       <c r="P5" t="n">
-        <v>348.6859328549492</v>
+        <v>348.6062504314062</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36979,28 +37171,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.847677352066861</v>
+        <v>0.8562128191753929</v>
       </c>
       <c r="J6" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K6" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3021561806398123</v>
+        <v>0.3076363349894227</v>
       </c>
       <c r="M6" t="n">
-        <v>8.089454599270098</v>
+        <v>8.083475330101686</v>
       </c>
       <c r="N6" t="n">
-        <v>103.0351669875754</v>
+        <v>102.933259631592</v>
       </c>
       <c r="O6" t="n">
-        <v>10.15062397035647</v>
+        <v>10.14560297033114</v>
       </c>
       <c r="P6" t="n">
-        <v>354.8116828167393</v>
+        <v>354.723660776302</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37057,28 +37249,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7602310456699863</v>
+        <v>0.7720273644013973</v>
       </c>
       <c r="J7" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K7" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2363147263418427</v>
+        <v>0.2424469226220071</v>
       </c>
       <c r="M7" t="n">
-        <v>8.968735965778009</v>
+        <v>8.976732194205169</v>
       </c>
       <c r="N7" t="n">
-        <v>114.7838839835419</v>
+        <v>115.0094938270857</v>
       </c>
       <c r="O7" t="n">
-        <v>10.71372409498872</v>
+        <v>10.7242479375985</v>
       </c>
       <c r="P7" t="n">
-        <v>356.0539055899861</v>
+        <v>355.9312577650205</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37135,28 +37327,28 @@
         <v>0.0559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6551015652828555</v>
+        <v>0.6681639940534244</v>
       </c>
       <c r="J8" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K8" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2309827184308438</v>
+        <v>0.2377847506719012</v>
       </c>
       <c r="M8" t="n">
-        <v>7.630491978163534</v>
+        <v>7.665571176332604</v>
       </c>
       <c r="N8" t="n">
-        <v>88.70976946503914</v>
+        <v>89.28025174734194</v>
       </c>
       <c r="O8" t="n">
-        <v>9.418586383584277</v>
+        <v>9.448822770448281</v>
       </c>
       <c r="P8" t="n">
-        <v>354.8931980578357</v>
+        <v>354.7584861674429</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37213,28 +37405,28 @@
         <v>0.1309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8983197695651519</v>
+        <v>0.9111565830852267</v>
       </c>
       <c r="J9" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K9" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4336370574464724</v>
+        <v>0.4393429030859148</v>
       </c>
       <c r="M9" t="n">
-        <v>6.327921972785289</v>
+        <v>6.373139970374</v>
       </c>
       <c r="N9" t="n">
-        <v>65.43768407637315</v>
+        <v>66.09603050293109</v>
       </c>
       <c r="O9" t="n">
-        <v>8.089356221379619</v>
+        <v>8.129946525219651</v>
       </c>
       <c r="P9" t="n">
-        <v>347.0720830687171</v>
+        <v>346.9396971431977</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37291,28 +37483,28 @@
         <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>0.704118445870607</v>
+        <v>0.7172965276629286</v>
       </c>
       <c r="J10" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K10" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L10" t="n">
-        <v>0.325984092091542</v>
+        <v>0.3327578603410883</v>
       </c>
       <c r="M10" t="n">
-        <v>6.344937642252024</v>
+        <v>6.394921153483809</v>
       </c>
       <c r="N10" t="n">
-        <v>63.35707886411432</v>
+        <v>64.07416103194815</v>
       </c>
       <c r="O10" t="n">
-        <v>7.959716003986218</v>
+        <v>8.004633722535226</v>
       </c>
       <c r="P10" t="n">
-        <v>352.1165850855526</v>
+        <v>351.9801757295151</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37369,28 +37561,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6702430212780576</v>
+        <v>0.6809999195482879</v>
       </c>
       <c r="J11" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K11" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2787846223951289</v>
+        <v>0.2853111347129383</v>
       </c>
       <c r="M11" t="n">
-        <v>7.168177341646194</v>
+        <v>7.199625752648794</v>
       </c>
       <c r="N11" t="n">
-        <v>71.82749611600079</v>
+        <v>72.14774211755019</v>
       </c>
       <c r="O11" t="n">
-        <v>8.4751103896056</v>
+        <v>8.493982700568102</v>
       </c>
       <c r="P11" t="n">
-        <v>355.7433725925223</v>
+        <v>355.6320263824862</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37447,28 +37639,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8811605231634915</v>
+        <v>0.8906340977658356</v>
       </c>
       <c r="J12" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K12" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2589928378204317</v>
+        <v>0.2643141808991173</v>
       </c>
       <c r="M12" t="n">
-        <v>9.469700020234356</v>
+        <v>9.473821159970212</v>
       </c>
       <c r="N12" t="n">
-        <v>137.7587541346003</v>
+        <v>137.5690545063034</v>
       </c>
       <c r="O12" t="n">
-        <v>11.73706752705293</v>
+        <v>11.7289835240017</v>
       </c>
       <c r="P12" t="n">
-        <v>351.7418673417516</v>
+        <v>351.6438651496035</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37525,28 +37717,28 @@
         <v>0.0624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6043845721970883</v>
+        <v>0.6150973253242491</v>
       </c>
       <c r="J13" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K13" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1101751699824609</v>
+        <v>0.11430420094322</v>
       </c>
       <c r="M13" t="n">
-        <v>9.617355555767229</v>
+        <v>9.630608768225846</v>
       </c>
       <c r="N13" t="n">
-        <v>182.9456222219866</v>
+        <v>182.667071358102</v>
       </c>
       <c r="O13" t="n">
-        <v>13.52573924863209</v>
+        <v>13.51543825993453</v>
       </c>
       <c r="P13" t="n">
-        <v>355.2491760601849</v>
+        <v>355.1383553033186</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37603,28 +37795,28 @@
         <v>0.0541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4667815461513803</v>
+        <v>0.4719622694311386</v>
       </c>
       <c r="J14" t="n">
+        <v>564</v>
+      </c>
+      <c r="K14" t="n">
         <v>561</v>
       </c>
-      <c r="K14" t="n">
-        <v>558</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.07931029714104743</v>
+        <v>0.08161735701751938</v>
       </c>
       <c r="M14" t="n">
-        <v>9.532225092993455</v>
+        <v>9.509802553469303</v>
       </c>
       <c r="N14" t="n">
-        <v>156.6391537393323</v>
+        <v>155.9655885132633</v>
       </c>
       <c r="O14" t="n">
-        <v>12.51555646942366</v>
+        <v>12.48861835886033</v>
       </c>
       <c r="P14" t="n">
-        <v>355.0077680516052</v>
+        <v>354.9541535217317</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37681,28 +37873,28 @@
         <v>0.0557</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2402784448135868</v>
+        <v>0.2408236461797851</v>
       </c>
       <c r="J15" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K15" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02865731507859004</v>
+        <v>0.02906872652316705</v>
       </c>
       <c r="M15" t="n">
-        <v>8.162955145768317</v>
+        <v>8.122894272473648</v>
       </c>
       <c r="N15" t="n">
-        <v>121.4966112970512</v>
+        <v>120.8527045217752</v>
       </c>
       <c r="O15" t="n">
-        <v>11.02255012676519</v>
+        <v>10.99330271218687</v>
       </c>
       <c r="P15" t="n">
-        <v>359.3745601318415</v>
+        <v>359.3689401855442</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37740,7 +37932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P562"/>
+  <dimension ref="A1:P565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83767,6 +83959,252 @@
         </is>
       </c>
     </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-40.78956289209829,172.210540163705</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-40.788982527783205,172.21104376047217</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-40.788320079212596,172.21127436579218</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-40.78767064722351,172.21154828465623</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-40.78702949082033,172.2118032438628</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-40.78638867545046,172.2120315136559</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-40.785742789536,172.212299935478</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-40.78509172545755,172.21256021331197</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>-40.784435403461266,172.21279621154738</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>-40.783784600738144,172.21303376277982</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>-40.78313177574677,172.2132430461348</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>-40.782475738801914,172.2134649356046</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>-40.78183163850527,172.21377455707815</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>-40.781180998014825,172.21404651150797</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:18:39+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-40.78956087077895,172.21053344083046</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-40.78898415144711,172.21104916077743</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-40.78832037743551,172.21127535767573</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-40.78767193951644,172.21155258277997</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-40.7870312162922,172.2118097321521</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-40.78638959290447,172.21203560591348</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-40.78574426882305,172.21230677482723</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-40.78509248975023,172.21256374694352</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>-40.784437030654445,172.2128037346931</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>-40.78378604243836,172.21304086143718</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>-40.783132655405204,172.21324788714406</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>-40.78247736211329,172.21347429423454</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>-40.78183314155259,172.21378322239858</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>-40.781182040116626,172.2140525194084</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-40.789551228086246,172.21050136941847</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-40.7889829585512,172.2110451932062</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-40.7883172957983,172.21126510821287</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-40.787672569095015,172.2115546767378</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-40.78703279301616,172.2118156611064</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-40.78638969484381,172.2120360606088</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-40.785743233322165,172.21230198728273</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-40.78509160218451,172.21255964337143</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-40.78443668549229,172.21280213887428</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>-40.7837861819577,172.21304154840405</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>-40.78313223652027,172.21324558190153</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>-40.782476540437244,172.21346955715018</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>-40.78183238000869,172.21377883196953</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>-40.781182481005764,172.21405506121246</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0322/nzd0322.xlsx
+++ b/data/nzd0322/nzd0322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P565"/>
+  <dimension ref="A1:P569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30936,6 +30936,222 @@
       <c r="P565" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>389.43</v>
+      </c>
+      <c r="C566" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="D566" t="n">
+        <v>378.34</v>
+      </c>
+      <c r="E566" t="n">
+        <v>380.96</v>
+      </c>
+      <c r="F566" t="n">
+        <v>386.01</v>
+      </c>
+      <c r="G566" t="n">
+        <v>388.89</v>
+      </c>
+      <c r="H566" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="I566" t="n">
+        <v>385</v>
+      </c>
+      <c r="J566" t="n">
+        <v>385.11</v>
+      </c>
+      <c r="K566" t="n">
+        <v>384.94</v>
+      </c>
+      <c r="L566" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="M566" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="N566" t="n">
+        <v>373.28</v>
+      </c>
+      <c r="O566" t="n">
+        <v>364.56</v>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>391.02</v>
+      </c>
+      <c r="C567" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="D567" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="E567" t="n">
+        <v>379.97</v>
+      </c>
+      <c r="F567" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="G567" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="H567" t="n">
+        <v>384.86</v>
+      </c>
+      <c r="I567" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="J567" t="n">
+        <v>384.54</v>
+      </c>
+      <c r="K567" t="n">
+        <v>384.23</v>
+      </c>
+      <c r="L567" t="n">
+        <v>384.52</v>
+      </c>
+      <c r="M567" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="N567" t="n">
+        <v>373.55</v>
+      </c>
+      <c r="O567" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:19:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>393.04</v>
+      </c>
+      <c r="C568" t="n">
+        <v>367.01</v>
+      </c>
+      <c r="D568" t="n">
+        <v>376.77</v>
+      </c>
+      <c r="E568" t="n">
+        <v>379.7</v>
+      </c>
+      <c r="F568" t="n">
+        <v>384.68</v>
+      </c>
+      <c r="G568" t="n">
+        <v>386.85</v>
+      </c>
+      <c r="H568" t="n">
+        <v>385.11</v>
+      </c>
+      <c r="I568" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="J568" t="n">
+        <v>384.53</v>
+      </c>
+      <c r="K568" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="L568" t="n">
+        <v>384.64</v>
+      </c>
+      <c r="M568" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="N568" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="O568" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>393.84</v>
+      </c>
+      <c r="C569" t="n">
+        <v>366.21</v>
+      </c>
+      <c r="D569" t="n">
+        <v>375.45</v>
+      </c>
+      <c r="E569" t="n">
+        <v>379.49</v>
+      </c>
+      <c r="F569" t="n">
+        <v>384.55</v>
+      </c>
+      <c r="G569" t="n">
+        <v>385.73</v>
+      </c>
+      <c r="H569" t="n">
+        <v>383.81</v>
+      </c>
+      <c r="I569" t="n">
+        <v>384.85</v>
+      </c>
+      <c r="J569" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="K569" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="L569" t="n">
+        <v>383.05</v>
+      </c>
+      <c r="M569" t="n">
+        <v>380.52</v>
+      </c>
+      <c r="N569" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="O569" t="n">
+        <v>364.03</v>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30950,7 +31166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36683,6 +36899,46 @@
       </c>
       <c r="B573" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -36851,28 +37107,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1697989103476295</v>
+        <v>-0.164530226631714</v>
       </c>
       <c r="J2" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K2" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01888725445269246</v>
+        <v>0.01795983042745686</v>
       </c>
       <c r="M2" t="n">
-        <v>7.900145360038558</v>
+        <v>7.873126020864457</v>
       </c>
       <c r="N2" t="n">
-        <v>93.43627564413484</v>
+        <v>92.92863499719441</v>
       </c>
       <c r="O2" t="n">
-        <v>9.66624413327818</v>
+        <v>9.639949947857323</v>
       </c>
       <c r="P2" t="n">
-        <v>392.0840833615973</v>
+        <v>392.029566199328</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36933,28 +37189,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5620141490886296</v>
+        <v>0.5618768877272547</v>
       </c>
       <c r="J3" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K3" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1487632825689811</v>
+        <v>0.1503961962615348</v>
       </c>
       <c r="M3" t="n">
-        <v>8.4563671173991</v>
+        <v>8.401455881215405</v>
       </c>
       <c r="N3" t="n">
-        <v>112.757315885526</v>
+        <v>111.9677825412177</v>
       </c>
       <c r="O3" t="n">
-        <v>10.6187247768047</v>
+        <v>10.58148300292628</v>
       </c>
       <c r="P3" t="n">
-        <v>352.1615548565282</v>
+        <v>352.1629861994589</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -37015,28 +37271,28 @@
         <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7658619791175848</v>
+        <v>0.7688804565311594</v>
       </c>
       <c r="J4" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K4" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2227219783636698</v>
+        <v>0.2263498878233136</v>
       </c>
       <c r="M4" t="n">
-        <v>8.728591521821482</v>
+        <v>8.680206671360281</v>
       </c>
       <c r="N4" t="n">
-        <v>127.7056072437825</v>
+        <v>126.8566092048637</v>
       </c>
       <c r="O4" t="n">
-        <v>11.30069056490719</v>
+        <v>11.26306393504288</v>
       </c>
       <c r="P4" t="n">
-        <v>353.6321083251486</v>
+        <v>353.6009043905336</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37093,28 +37349,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9054777376070011</v>
+        <v>0.9139856193568183</v>
       </c>
       <c r="J5" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K5" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3111376028961012</v>
+        <v>0.3173976455797575</v>
       </c>
       <c r="M5" t="n">
-        <v>8.388159738241777</v>
+        <v>8.367198063301231</v>
       </c>
       <c r="N5" t="n">
-        <v>113.2481630593856</v>
+        <v>112.7908713022051</v>
       </c>
       <c r="O5" t="n">
-        <v>10.6418120195475</v>
+        <v>10.6203046708748</v>
       </c>
       <c r="P5" t="n">
-        <v>348.6062504314062</v>
+        <v>348.5182658027414</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37171,28 +37427,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8562128191753929</v>
+        <v>0.8649812895357439</v>
       </c>
       <c r="J6" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K6" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3076363349894227</v>
+        <v>0.3141090119872888</v>
       </c>
       <c r="M6" t="n">
-        <v>8.083475330101686</v>
+        <v>8.064448298072488</v>
       </c>
       <c r="N6" t="n">
-        <v>102.933259631592</v>
+        <v>102.5697440685524</v>
       </c>
       <c r="O6" t="n">
-        <v>10.14560297033114</v>
+        <v>10.12767219397194</v>
       </c>
       <c r="P6" t="n">
-        <v>354.723660776302</v>
+        <v>354.6329808591424</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37249,28 +37505,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7720273644013973</v>
+        <v>0.7846400512746974</v>
       </c>
       <c r="J7" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K7" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2424469226220071</v>
+        <v>0.249746798105594</v>
       </c>
       <c r="M7" t="n">
-        <v>8.976732194205169</v>
+        <v>8.973033188629351</v>
       </c>
       <c r="N7" t="n">
-        <v>115.0094938270857</v>
+        <v>114.9387010407934</v>
       </c>
       <c r="O7" t="n">
-        <v>10.7242479375985</v>
+        <v>10.72094683508846</v>
       </c>
       <c r="P7" t="n">
-        <v>355.9312577650205</v>
+        <v>355.7997643311435</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37327,28 +37583,28 @@
         <v>0.0559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6681639940534244</v>
+        <v>0.6831630712671236</v>
       </c>
       <c r="J8" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K8" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2377847506719012</v>
+        <v>0.2462046511539115</v>
       </c>
       <c r="M8" t="n">
-        <v>7.665571176332604</v>
+        <v>7.697875675482662</v>
       </c>
       <c r="N8" t="n">
-        <v>89.28025174734194</v>
+        <v>89.70922611812749</v>
       </c>
       <c r="O8" t="n">
-        <v>9.448822770448281</v>
+        <v>9.471495453101769</v>
       </c>
       <c r="P8" t="n">
-        <v>354.7584861674429</v>
+        <v>354.6033725767759</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37405,28 +37661,28 @@
         <v>0.1309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9111565830852267</v>
+        <v>0.9275680009116093</v>
       </c>
       <c r="J9" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K9" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4393429030859148</v>
+        <v>0.4467700649645643</v>
       </c>
       <c r="M9" t="n">
-        <v>6.373139970374</v>
+        <v>6.430660411845137</v>
       </c>
       <c r="N9" t="n">
-        <v>66.09603050293109</v>
+        <v>66.88739259714363</v>
       </c>
       <c r="O9" t="n">
-        <v>8.129946525219651</v>
+        <v>8.178471287297134</v>
       </c>
       <c r="P9" t="n">
-        <v>346.9396971431977</v>
+        <v>346.7699631850431</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37483,28 +37739,28 @@
         <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7172965276629286</v>
+        <v>0.7334549784017766</v>
       </c>
       <c r="J10" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K10" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3327578603410883</v>
+        <v>0.3414875638046725</v>
       </c>
       <c r="M10" t="n">
-        <v>6.394921153483809</v>
+        <v>6.453089256435593</v>
       </c>
       <c r="N10" t="n">
-        <v>64.07416103194815</v>
+        <v>64.83429287975616</v>
       </c>
       <c r="O10" t="n">
-        <v>8.004633722535226</v>
+        <v>8.051974470883286</v>
       </c>
       <c r="P10" t="n">
-        <v>351.9801757295151</v>
+        <v>351.8124417995722</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37561,28 +37817,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6809999195482879</v>
+        <v>0.693566599862426</v>
       </c>
       <c r="J11" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K11" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2853111347129383</v>
+        <v>0.2934878225483298</v>
       </c>
       <c r="M11" t="n">
-        <v>7.199625752648794</v>
+        <v>7.229571228412992</v>
       </c>
       <c r="N11" t="n">
-        <v>72.14774211755019</v>
+        <v>72.37268333012329</v>
       </c>
       <c r="O11" t="n">
-        <v>8.493982700568102</v>
+        <v>8.507213605530502</v>
       </c>
       <c r="P11" t="n">
-        <v>355.6320263824862</v>
+        <v>355.5015790176535</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37639,28 +37895,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8906340977658356</v>
+        <v>0.9014359241106837</v>
       </c>
       <c r="J12" t="n">
+        <v>568</v>
+      </c>
+      <c r="K12" t="n">
         <v>564</v>
       </c>
-      <c r="K12" t="n">
-        <v>560</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2643141808991173</v>
+        <v>0.2708647509332482</v>
       </c>
       <c r="M12" t="n">
-        <v>9.473821159970212</v>
+        <v>9.469201026986058</v>
       </c>
       <c r="N12" t="n">
-        <v>137.5690545063034</v>
+        <v>137.14546758682</v>
       </c>
       <c r="O12" t="n">
-        <v>11.7289835240017</v>
+        <v>11.71091232939689</v>
       </c>
       <c r="P12" t="n">
-        <v>351.6438651496035</v>
+        <v>351.5318145074861</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37717,28 +37973,28 @@
         <v>0.0624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6150973253242491</v>
+        <v>0.6274324239074707</v>
       </c>
       <c r="J13" t="n">
+        <v>568</v>
+      </c>
+      <c r="K13" t="n">
         <v>564</v>
       </c>
-      <c r="K13" t="n">
-        <v>560</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.11430420094322</v>
+        <v>0.1193711402065064</v>
       </c>
       <c r="M13" t="n">
-        <v>9.630608768225846</v>
+        <v>9.636116673523194</v>
       </c>
       <c r="N13" t="n">
-        <v>182.667071358102</v>
+        <v>182.0889626114758</v>
       </c>
       <c r="O13" t="n">
-        <v>13.51543825993453</v>
+        <v>13.49403433415951</v>
       </c>
       <c r="P13" t="n">
-        <v>355.1383553033186</v>
+        <v>355.0103968590982</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37795,28 +38051,28 @@
         <v>0.0541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4719622694311386</v>
+        <v>0.4793520182444961</v>
       </c>
       <c r="J14" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K14" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08161735701751938</v>
+        <v>0.08488227055279995</v>
       </c>
       <c r="M14" t="n">
-        <v>9.509802553469303</v>
+        <v>9.483113216035976</v>
       </c>
       <c r="N14" t="n">
-        <v>155.9655885132633</v>
+        <v>155.1167999833916</v>
       </c>
       <c r="O14" t="n">
-        <v>12.48861835886033</v>
+        <v>12.4545895148492</v>
       </c>
       <c r="P14" t="n">
-        <v>354.9541535217317</v>
+        <v>354.8774506690091</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37873,28 +38129,28 @@
         <v>0.0557</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2408236461797851</v>
+        <v>0.2386667946677148</v>
       </c>
       <c r="J15" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K15" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02906872652316705</v>
+        <v>0.02893320205796601</v>
       </c>
       <c r="M15" t="n">
-        <v>8.122894272473648</v>
+        <v>8.077040885194348</v>
       </c>
       <c r="N15" t="n">
-        <v>120.8527045217752</v>
+        <v>120.0239047602103</v>
       </c>
       <c r="O15" t="n">
-        <v>10.99330271218687</v>
+        <v>10.95554219380357</v>
       </c>
       <c r="P15" t="n">
-        <v>359.3689401855442</v>
+        <v>359.3912505355896</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37932,7 +38188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P565"/>
+  <dimension ref="A1:P569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84205,6 +84461,334 @@
         </is>
       </c>
     </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-40.78954589312187,172.21048362544542</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-40.78898179879118,172.21104133584538</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-40.78831500942173,172.2112575037733</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-40.787672502823575,172.21155445632115</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-40.78703365575178,172.21181890525133</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>-40.78638997517694,172.21203731102085</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-40.78574328263173,172.21230221526105</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-40.7850922185496,172.21256249307424</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>-40.78443671014673,172.21280225286134</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>-40.783786577262504,172.21304349481017</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>-40.783131754802525,172.2132429308727</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>-40.78247603941518,172.2134666686842</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>-40.78183211948049,172.21377732998064</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>-40.78118558726852,172.21407296937855</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-40.78954062442769,172.21046610189723</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-40.788985642566786,172.21105412024167</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-40.788320973881305,172.21127734144287</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-40.78767578325863,172.21156536694394</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-40.78703701744491,172.2118315462307</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-40.786395556352055,172.2120622055907</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-40.78574779445555,172.21232307527742</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-40.785091774766755,172.21256044128822</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>-40.78443811544962,172.2128087501238</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>-40.78378822824105,172.21305162391832</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>-40.783134603219565,172.21325860652215</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>-40.782479426322965,172.21348619471522</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>-40.78183157838336,172.21377421046535</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>-40.7811867295709,172.21407955496267</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:19:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-40.789533930862724,172.2104438392803</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-40.78898637155854,172.21105654486874</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-40.78832021175612,172.21127480662932</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-40.78767667792257,172.21156834256857</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>-40.78703761243471,172.2118337835723</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>-40.78639517407995,172.21206050048306</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>-40.7857471780864,172.21232022554824</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-40.78509214458581,172.21256215110992</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>-40.78443814010405,172.21280886411088</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>-40.78378815848141,172.21305128043488</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>-40.78313435188874,172.21325722337653</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>-40.782478805056094,172.21348261301708</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>-40.78183129781445,172.2137725929389</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>-40.78118713037867,172.214081865694</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-40.789531279944725,172.21043502240354</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-40.78898902243728,172.21106536169486</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-40.78832458569131,172.2112893542556</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>-40.78767737377223,172.21157065694328</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>-40.78703799917805,172.2118352378444</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>-40.786398028377675,172.21207323195407</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>-40.78575038320524,172.2123350441406</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-40.78509258836864,172.21256420289598</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>-40.78443924955344,172.2128139935288</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>-40.78378932114203,172.21305700515916</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>-40.7831376820209,172.21327555005655</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>-40.782481610776514,172.21349878842867</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>-40.78182981480698,172.21376404315657</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>-40.78118664940934,172.2140790928164</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0322/nzd0322.xlsx
+++ b/data/nzd0322/nzd0322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P569"/>
+  <dimension ref="A1:P574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31152,6 +31152,276 @@
       <c r="P569" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>393.49</v>
+      </c>
+      <c r="C570" t="n">
+        <v>366.27</v>
+      </c>
+      <c r="D570" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="E570" t="n">
+        <v>379.19</v>
+      </c>
+      <c r="F570" t="n">
+        <v>384.42</v>
+      </c>
+      <c r="G570" t="n">
+        <v>385.72</v>
+      </c>
+      <c r="H570" t="n">
+        <v>383.5</v>
+      </c>
+      <c r="I570" t="n">
+        <v>383.7</v>
+      </c>
+      <c r="J570" t="n">
+        <v>383.04</v>
+      </c>
+      <c r="K570" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="L570" t="n">
+        <v>382.54</v>
+      </c>
+      <c r="M570" t="n">
+        <v>380.28</v>
+      </c>
+      <c r="N570" t="n">
+        <v>373.85</v>
+      </c>
+      <c r="O570" t="n">
+        <v>362.47</v>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:19:09+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>393.3</v>
+      </c>
+      <c r="C571" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="D571" t="n">
+        <v>374.49</v>
+      </c>
+      <c r="E571" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="F571" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="G571" t="n">
+        <v>383.44</v>
+      </c>
+      <c r="H571" t="n">
+        <v>381.13</v>
+      </c>
+      <c r="I571" t="n">
+        <v>381.85</v>
+      </c>
+      <c r="J571" t="n">
+        <v>381.77</v>
+      </c>
+      <c r="K571" t="n">
+        <v>382.53</v>
+      </c>
+      <c r="L571" t="n">
+        <v>381.76</v>
+      </c>
+      <c r="M571" t="n">
+        <v>379.32</v>
+      </c>
+      <c r="N571" t="n">
+        <v>372.19</v>
+      </c>
+      <c r="O571" t="n">
+        <v>361.04</v>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>392.24</v>
+      </c>
+      <c r="C572" t="n">
+        <v>363.33</v>
+      </c>
+      <c r="D572" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="E572" t="n">
+        <v>376.41</v>
+      </c>
+      <c r="F572" t="n">
+        <v>382.05</v>
+      </c>
+      <c r="G572" t="n">
+        <v>383.21</v>
+      </c>
+      <c r="H572" t="n">
+        <v>379.98</v>
+      </c>
+      <c r="I572" t="n">
+        <v>381.11</v>
+      </c>
+      <c r="J572" t="n">
+        <v>381.22</v>
+      </c>
+      <c r="K572" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="L572" t="n">
+        <v>380.91</v>
+      </c>
+      <c r="M572" t="n">
+        <v>378.87</v>
+      </c>
+      <c r="N572" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="O572" t="n">
+        <v>361.31</v>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>392.8</v>
+      </c>
+      <c r="C573" t="n">
+        <v>361.75</v>
+      </c>
+      <c r="D573" t="n">
+        <v>372.46</v>
+      </c>
+      <c r="E573" t="n">
+        <v>375.39</v>
+      </c>
+      <c r="F573" t="n">
+        <v>380.96</v>
+      </c>
+      <c r="G573" t="n">
+        <v>381.64</v>
+      </c>
+      <c r="H573" t="n">
+        <v>378.23</v>
+      </c>
+      <c r="I573" t="n">
+        <v>380.19</v>
+      </c>
+      <c r="J573" t="n">
+        <v>380.23</v>
+      </c>
+      <c r="K573" t="n">
+        <v>380.82</v>
+      </c>
+      <c r="L573" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="M573" t="n">
+        <v>377.71</v>
+      </c>
+      <c r="N573" t="n">
+        <v>370.3</v>
+      </c>
+      <c r="O573" t="n">
+        <v>359.72</v>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>391.58</v>
+      </c>
+      <c r="C574" t="n">
+        <v>361.33</v>
+      </c>
+      <c r="D574" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="E574" t="n">
+        <v>374.46</v>
+      </c>
+      <c r="F574" t="n">
+        <v>380.32</v>
+      </c>
+      <c r="G574" t="n">
+        <v>380.58</v>
+      </c>
+      <c r="H574" t="n">
+        <v>377</v>
+      </c>
+      <c r="I574" t="n">
+        <v>378.87</v>
+      </c>
+      <c r="J574" t="n">
+        <v>379.33</v>
+      </c>
+      <c r="K574" t="n">
+        <v>380.28</v>
+      </c>
+      <c r="L574" t="n">
+        <v>379.61</v>
+      </c>
+      <c r="M574" t="n">
+        <v>377.69</v>
+      </c>
+      <c r="N574" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="O574" t="n">
+        <v>360.04</v>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31166,7 +31436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B577"/>
+  <dimension ref="A1:B582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36939,6 +37209,56 @@
       </c>
       <c r="B577" t="n">
         <v>-0.83</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
@@ -37107,28 +37427,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.164530226631714</v>
+        <v>-0.1568884534305229</v>
       </c>
       <c r="J2" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K2" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01795983042745686</v>
+        <v>0.01658461993618576</v>
       </c>
       <c r="M2" t="n">
-        <v>7.873126020864457</v>
+        <v>7.845704997736428</v>
       </c>
       <c r="N2" t="n">
-        <v>92.92863499719441</v>
+        <v>92.3440596642908</v>
       </c>
       <c r="O2" t="n">
-        <v>9.639949947857323</v>
+        <v>9.609581659171788</v>
       </c>
       <c r="P2" t="n">
-        <v>392.029566199328</v>
+        <v>391.9501264402753</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -37189,28 +37509,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5618768877272547</v>
+        <v>0.5558239140983658</v>
       </c>
       <c r="J3" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K3" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1503961962615348</v>
+        <v>0.1495482851094415</v>
       </c>
       <c r="M3" t="n">
-        <v>8.401455881215405</v>
+        <v>8.363424137078391</v>
       </c>
       <c r="N3" t="n">
-        <v>111.9677825412177</v>
+        <v>111.1573557607238</v>
       </c>
       <c r="O3" t="n">
-        <v>10.58148300292628</v>
+        <v>10.54311888203504</v>
       </c>
       <c r="P3" t="n">
-        <v>352.1629861994589</v>
+        <v>352.2259599198181</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -37271,28 +37591,28 @@
         <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7688804565311594</v>
+        <v>0.7678703296021983</v>
       </c>
       <c r="J4" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K4" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2263498878233136</v>
+        <v>0.2287616230840359</v>
       </c>
       <c r="M4" t="n">
-        <v>8.680206671360281</v>
+        <v>8.616935589580502</v>
       </c>
       <c r="N4" t="n">
-        <v>126.8566092048637</v>
+        <v>125.7699137895034</v>
       </c>
       <c r="O4" t="n">
-        <v>11.26306393504288</v>
+        <v>11.2147186228413</v>
       </c>
       <c r="P4" t="n">
-        <v>353.6009043905336</v>
+        <v>353.6114374493689</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37349,28 +37669,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9139856193568183</v>
+        <v>0.9189042386639329</v>
       </c>
       <c r="J5" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K5" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3173976455797575</v>
+        <v>0.3231022768524835</v>
       </c>
       <c r="M5" t="n">
-        <v>8.367198063301231</v>
+        <v>8.315809351814661</v>
       </c>
       <c r="N5" t="n">
-        <v>112.7908713022051</v>
+        <v>111.9229300990871</v>
       </c>
       <c r="O5" t="n">
-        <v>10.6203046708748</v>
+        <v>10.57936340708112</v>
       </c>
       <c r="P5" t="n">
-        <v>348.5182658027414</v>
+        <v>348.4671638107533</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37427,28 +37747,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8649812895357439</v>
+        <v>0.8710743443422898</v>
       </c>
       <c r="J6" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K6" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3141090119872888</v>
+        <v>0.3203847479670476</v>
       </c>
       <c r="M6" t="n">
-        <v>8.064448298072488</v>
+        <v>8.019942922639695</v>
       </c>
       <c r="N6" t="n">
-        <v>102.5697440685524</v>
+        <v>101.8350441153196</v>
       </c>
       <c r="O6" t="n">
-        <v>10.12767219397194</v>
+        <v>10.09133510073467</v>
       </c>
       <c r="P6" t="n">
-        <v>354.6329808591424</v>
+        <v>354.5696637451457</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37505,28 +37825,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7846400512746974</v>
+        <v>0.7934949644498334</v>
       </c>
       <c r="J7" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K7" t="n">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="L7" t="n">
-        <v>0.249746798105594</v>
+        <v>0.2565896431062632</v>
       </c>
       <c r="M7" t="n">
-        <v>8.973033188629351</v>
+        <v>8.936060481112298</v>
       </c>
       <c r="N7" t="n">
-        <v>114.9387010407934</v>
+        <v>114.2541337532387</v>
       </c>
       <c r="O7" t="n">
-        <v>10.72094683508846</v>
+        <v>10.6889725302874</v>
       </c>
       <c r="P7" t="n">
-        <v>355.7997643311435</v>
+        <v>355.7069932785854</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37583,28 +37903,28 @@
         <v>0.0559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6831630712671236</v>
+        <v>0.6934308671082485</v>
       </c>
       <c r="J8" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K8" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2462046511539115</v>
+        <v>0.2539561408292222</v>
       </c>
       <c r="M8" t="n">
-        <v>7.697875675482662</v>
+        <v>7.688880703446464</v>
       </c>
       <c r="N8" t="n">
-        <v>89.70922611812749</v>
+        <v>89.37324103214428</v>
       </c>
       <c r="O8" t="n">
-        <v>9.471495453101769</v>
+        <v>9.453742170809624</v>
       </c>
       <c r="P8" t="n">
-        <v>354.6033725767759</v>
+        <v>354.496668514512</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37661,28 +37981,28 @@
         <v>0.1309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9275680009116093</v>
+        <v>0.9414125337150091</v>
       </c>
       <c r="J9" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K9" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4467700649645643</v>
+        <v>0.4553997261552439</v>
       </c>
       <c r="M9" t="n">
-        <v>6.430660411845137</v>
+        <v>6.460392106816876</v>
       </c>
       <c r="N9" t="n">
-        <v>66.88739259714363</v>
+        <v>67.05645174529488</v>
       </c>
       <c r="O9" t="n">
-        <v>8.178471287297134</v>
+        <v>8.188800384995037</v>
       </c>
       <c r="P9" t="n">
-        <v>346.7699631850431</v>
+        <v>346.6260570924413</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37739,28 +38059,28 @@
         <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7334549784017766</v>
+        <v>0.7476359679812714</v>
       </c>
       <c r="J10" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K10" t="n">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3414875638046725</v>
+        <v>0.3511874508736574</v>
       </c>
       <c r="M10" t="n">
-        <v>6.453089256435593</v>
+        <v>6.48606733150486</v>
       </c>
       <c r="N10" t="n">
-        <v>64.83429287975616</v>
+        <v>65.0425256282284</v>
       </c>
       <c r="O10" t="n">
-        <v>8.051974470883286</v>
+        <v>8.064894644583301</v>
       </c>
       <c r="P10" t="n">
-        <v>351.8124417995722</v>
+        <v>351.6644848127435</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37817,28 +38137,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.693566599862426</v>
+        <v>0.7046557737449846</v>
       </c>
       <c r="J11" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K11" t="n">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2934878225483298</v>
+        <v>0.3022002353029558</v>
       </c>
       <c r="M11" t="n">
-        <v>7.229571228412992</v>
+        <v>7.236839946820271</v>
       </c>
       <c r="N11" t="n">
-        <v>72.37268333012329</v>
+        <v>72.21490111095743</v>
       </c>
       <c r="O11" t="n">
-        <v>8.507213605530502</v>
+        <v>8.497935108657716</v>
       </c>
       <c r="P11" t="n">
-        <v>355.5015790176535</v>
+        <v>355.3858806889592</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37895,28 +38215,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9014359241106837</v>
+        <v>0.9089740855607672</v>
       </c>
       <c r="J12" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K12" t="n">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2708647509332482</v>
+        <v>0.2771256845958324</v>
       </c>
       <c r="M12" t="n">
-        <v>9.469201026986058</v>
+        <v>9.428898037965824</v>
       </c>
       <c r="N12" t="n">
-        <v>137.14546758682</v>
+        <v>136.1673898052225</v>
       </c>
       <c r="O12" t="n">
-        <v>11.71091232939689</v>
+        <v>11.66907836143123</v>
       </c>
       <c r="P12" t="n">
-        <v>351.5318145074861</v>
+        <v>351.4532181386522</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37973,28 +38293,28 @@
         <v>0.0624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6274324239074707</v>
+        <v>0.6375963996504669</v>
       </c>
       <c r="J13" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K13" t="n">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1193711402065064</v>
+        <v>0.1243360803397831</v>
       </c>
       <c r="M13" t="n">
-        <v>9.636116673523194</v>
+        <v>9.611702196372269</v>
       </c>
       <c r="N13" t="n">
-        <v>182.0889626114758</v>
+        <v>180.890637492904</v>
       </c>
       <c r="O13" t="n">
-        <v>13.49403433415951</v>
+        <v>13.44955900737656</v>
       </c>
       <c r="P13" t="n">
-        <v>355.0103968590982</v>
+        <v>354.9044115868023</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38051,28 +38371,28 @@
         <v>0.0541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4793520182444961</v>
+        <v>0.4851354900910962</v>
       </c>
       <c r="J14" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K14" t="n">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08488227055279995</v>
+        <v>0.08800573570715398</v>
       </c>
       <c r="M14" t="n">
-        <v>9.483113216035976</v>
+        <v>9.431437709134139</v>
       </c>
       <c r="N14" t="n">
-        <v>155.1167999833916</v>
+        <v>153.8998274013663</v>
       </c>
       <c r="O14" t="n">
-        <v>12.4545895148492</v>
+        <v>12.40563692042316</v>
       </c>
       <c r="P14" t="n">
-        <v>354.8774506690091</v>
+        <v>354.8171384619452</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38129,28 +38449,28 @@
         <v>0.0557</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2386667946677148</v>
+        <v>0.2312727063612556</v>
       </c>
       <c r="J15" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K15" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02893320205796601</v>
+        <v>0.02760808162277029</v>
       </c>
       <c r="M15" t="n">
-        <v>8.077040885194348</v>
+        <v>8.04495675016868</v>
       </c>
       <c r="N15" t="n">
-        <v>120.0239047602103</v>
+        <v>119.1926299271492</v>
       </c>
       <c r="O15" t="n">
-        <v>10.95554219380357</v>
+        <v>10.91753772272618</v>
       </c>
       <c r="P15" t="n">
-        <v>359.3912505355896</v>
+        <v>359.4681490135779</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38188,7 +38508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P569"/>
+  <dimension ref="A1:P574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84789,6 +85109,416 @@
         </is>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-40.78953243972144,172.21043887978703</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-40.7889888236214,172.21106470043287</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-40.78832342593594,172.2112854969303</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>-40.787678367843114,172.211573963193</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>-40.78703838592138,172.2118366921165</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>-40.78639805386248,172.21207334562794</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>-40.78575114750252,172.21233857780513</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>-40.785095423646986,172.21257731152969</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>-40.78444181361336,172.21282584818428</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>-40.78379080934722,172.21306433280657</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>-40.78313875017589,172.213281428426</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>-40.782482091756926,172.2135015613565</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>-40.78183097716423,172.2137707443373</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>-40.78118977570876,172.21409711652137</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:19:09+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-40.789533069314444,172.21044097379527</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-40.788996378622244,172.211089828391</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-40.78832776673394,172.2112999343487</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>-40.7876844648091,172.2115942415267</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-40.78704290784196,172.2118536959145</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>-40.78640386439278,172.21209926326878</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-40.78575699067502,172.21236559324322</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-40.78509998474383,172.2125983993342</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>-40.78444494472337,172.21284032454366</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>-40.78379218128596,172.2130710879818</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>-40.78314038382412,172.21329041887378</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>-40.78248401567795,172.21351265306828</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>-40.78183430390875,172.21378992358</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>-40.781192641480764,172.21411363825248</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-40.78953658178004,172.21045265615774</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-40.78899856559515,172.21109710227472</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-40.7883297548851,172.21130654690737</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-40.78768757956209,172.21160460111167</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-40.78704543654647,172.21186320461834</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-40.786404450542456,172.2121018777679</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-40.78575982596743,172.21237870200184</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-40.785101809181484,172.2126068344568</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>-40.78444630071533,172.21284659383358</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>-40.78379436708585,172.21308185046496</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>-40.783142164081,172.21330021615714</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>-40.78248491751556,172.2135178523084</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>-40.78183458447741,172.2137915411066</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>-40.78119210039113,172.21411051876467</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-40.789534726137994,172.21044648434344</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-40.78900380107394,172.2111145155134</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-40.78833449331051,172.21132230684051</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>-40.78769095939939,172.21161584236455</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-40.78704867923699,172.21187539813374</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-40.78640845164948,172.21211972456746</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-40.78576414053999,172.21239865011498</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-40.78510407740043,172.21261732136668</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>-40.78444874150001,172.2128578785561</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>-40.78379615758078,172.21309066654214</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>-40.78314409094635,172.21331082027618</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>-40.78248724225143,172.21353125479467</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>-40.78183809158387,172.21381176019003</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>-40.78119528680669,172.21412888908245</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-40.789538768786336,172.21045993008218</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-40.78900519278303,172.21111914434948</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-40.788335653064664,172.21132616416716</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>-40.787694041014824,172.21162609174323</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-40.78705058320147,172.21188255762962</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-40.78641115303228,172.21213177400026</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-40.78576717306608,172.21241267079034</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-40.78510733179987,172.21263236780385</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>-40.78445096039422,172.21286813739547</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>-40.78379741325213,172.21309684924591</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>-40.78314488682523,172.21331520023855</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>-40.78248728233307,172.21353148587204</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>-40.78183837215223,172.2138133777168</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>-40.78119464551573,172.21412519191142</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
